--- a/data/trans_dic/P16A13-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A13-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,99</t>
+          <t>3,44; 6,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,86</t>
+          <t>5,36; 8,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,18</t>
+          <t>3,28; 6,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,54; 15,64</t>
+          <t>10,49; 15,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,87</t>
+          <t>4,36; 6,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,73; 9,8</t>
+          <t>6,82; 9,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 9,4</t>
+          <t>5,8; 9,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,65; 20,66</t>
+          <t>16,36; 20,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 5,99</t>
+          <t>4,29; 6,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,76</t>
+          <t>6,66; 8,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,5</t>
+          <t>5,09; 7,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,68; 17,68</t>
+          <t>14,69; 17,8</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,16</t>
+          <t>0,93; 2,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,74</t>
+          <t>2,11; 3,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,21</t>
+          <t>1,7; 3,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,72</t>
+          <t>3,17; 5,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,55</t>
+          <t>1,96; 3,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,25</t>
+          <t>2,34; 4,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,59</t>
+          <t>2,01; 3,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,24</t>
+          <t>3,75; 6,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,57</t>
+          <t>1,54; 2,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 3,62</t>
+          <t>2,44; 3,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,08</t>
+          <t>2,01; 3,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,75</t>
+          <t>3,94; 5,66</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,8</t>
+          <t>1,69; 4,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,22</t>
+          <t>2,02; 6,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,83</t>
+          <t>1,49; 4,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,46</t>
+          <t>4,24; 7,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,92</t>
+          <t>0,61; 2,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 7,89</t>
+          <t>3,41; 7,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,31</t>
+          <t>1,96; 5,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,15</t>
+          <t>3,53; 6,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,24</t>
+          <t>1,47; 3,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,13</t>
+          <t>3,2; 6,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,33</t>
+          <t>1,96; 4,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,3</t>
+          <t>4,2; 6,32</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,32</t>
+          <t>2,15; 3,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,98</t>
+          <t>3,46; 4,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,58</t>
+          <t>2,39; 3,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 6,99</t>
+          <t>4,6; 7,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 4,21</t>
+          <t>3,01; 4,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,17</t>
+          <t>4,68; 6,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 4,81</t>
+          <t>3,42; 4,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,59; 8,67</t>
+          <t>6,26; 8,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,53</t>
+          <t>2,72; 3,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 5,32</t>
+          <t>4,23; 5,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 4,05</t>
+          <t>3,09; 3,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 7,65</t>
+          <t>6,01; 7,7</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35298; 61845</t>
+          <t>35534; 62251</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50841; 85769</t>
+          <t>51902; 86587</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25113; 46651</t>
+          <t>24727; 47710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54190; 80364</t>
+          <t>53923; 80681</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>60014; 90294</t>
+          <t>57329; 91616</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89793; 130703</t>
+          <t>90908; 130133</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58041; 93534</t>
+          <t>57665; 93549</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>125185; 155409</t>
+          <t>123010; 153331</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100211; 140693</t>
+          <t>100670; 144423</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>151528; 201580</t>
+          <t>153407; 204693</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>87536; 131181</t>
+          <t>89042; 132399</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>185836; 223792</t>
+          <t>185966; 225323</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14807; 36552</t>
+          <t>15663; 36907</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41966; 73358</t>
+          <t>41275; 72720</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35937; 66712</t>
+          <t>35230; 66171</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71588; 130967</t>
+          <t>72493; 128812</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31000; 56341</t>
+          <t>31066; 56158</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42375; 74452</t>
+          <t>40912; 74819</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39742; 71398</t>
+          <t>40018; 68616</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83314; 139672</t>
+          <t>83963; 140056</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52356; 84269</t>
+          <t>50614; 83380</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89382; 134188</t>
+          <t>90636; 137830</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82983; 125031</t>
+          <t>81632; 123328</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>178926; 260210</t>
+          <t>178467; 256143</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9810; 26455</t>
+          <t>9323; 26517</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9211; 29888</t>
+          <t>9702; 29048</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7817; 26418</t>
+          <t>8123; 26055</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27085; 48238</t>
+          <t>27408; 48219</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2879; 13915</t>
+          <t>2912; 13681</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15343; 36100</t>
+          <t>15622; 35476</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9873; 29174</t>
+          <t>10748; 28768</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23445; 40604</t>
+          <t>23324; 40767</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14281; 33309</t>
+          <t>15062; 33215</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29112; 57463</t>
+          <t>30034; 57533</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22821; 47429</t>
+          <t>21516; 47589</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55936; 82373</t>
+          <t>54955; 82657</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70617; 108614</t>
+          <t>70576; 106821</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>118920; 169603</t>
+          <t>117935; 167980</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80501; 120900</t>
+          <t>80671; 118891</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>165461; 241383</t>
+          <t>158642; 242572</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>101921; 142388</t>
+          <t>101559; 142806</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>163920; 218766</t>
+          <t>165935; 221620</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>117570; 169868</t>
+          <t>120814; 171423</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>240468; 316408</t>
+          <t>228482; 318775</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>178837; 234861</t>
+          <t>181139; 237608</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>291310; 369802</t>
+          <t>293730; 370045</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>211615; 279675</t>
+          <t>213629; 275331</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>433925; 543076</t>
+          <t>426520; 546982</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A13-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A13-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,03</t>
+          <t>3,35; 5,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,94</t>
+          <t>5,33; 8,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,32</t>
+          <t>3,3; 6,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,49; 15,7</t>
+          <t>10,06; 14,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,97</t>
+          <t>4,32; 6,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 9,76</t>
+          <t>6,78; 9,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,41</t>
+          <t>5,79; 9,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,36; 20,39</t>
+          <t>16,15; 19,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 6,15</t>
+          <t>4,23; 6,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 8,89</t>
+          <t>6,63; 8,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,57</t>
+          <t>5,07; 7,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,69; 17,8</t>
+          <t>14,17; 17,18</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,18</t>
+          <t>0,9; 2,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,71</t>
+          <t>2,15; 3,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,19</t>
+          <t>1,72; 3,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,62</t>
+          <t>4,11; 5,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,54</t>
+          <t>1,87; 3,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,27</t>
+          <t>2,38; 4,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,45</t>
+          <t>1,99; 3,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,26</t>
+          <t>5,15; 6,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,54</t>
+          <t>1,6; 2,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 3,71</t>
+          <t>2,48; 3,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,03</t>
+          <t>1,99; 3,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 5,66</t>
+          <t>4,8; 6,0</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,81</t>
+          <t>1,53; 4,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,05</t>
+          <t>1,98; 6,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,76</t>
+          <t>1,44; 4,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,46</t>
+          <t>4,51; 7,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,87</t>
+          <t>0,61; 2,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 7,75</t>
+          <t>3,42; 7,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,24</t>
+          <t>1,8; 5,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,17</t>
+          <t>3,74; 6,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,23</t>
+          <t>1,46; 3,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,13</t>
+          <t>3,12; 6,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,34</t>
+          <t>1,96; 4,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,32</t>
+          <t>4,44; 6,46</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,26</t>
+          <t>2,14; 3,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,93</t>
+          <t>3,46; 4,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,52</t>
+          <t>2,39; 3,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,03</t>
+          <t>5,53; 7,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,23</t>
+          <t>3,02; 4,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,26</t>
+          <t>4,62; 6,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 4,85</t>
+          <t>3,45; 4,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 8,73</t>
+          <t>7,67; 9,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 3,57</t>
+          <t>2,74; 3,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,32</t>
+          <t>4,24; 5,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 3,98</t>
+          <t>3,1; 4,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 7,7</t>
+          <t>6,9; 7,88</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66402</t>
+          <t>70451</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>138401</t>
+          <t>147657</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>204803</t>
+          <t>218108</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35534; 62251</t>
+          <t>34532; 61573</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51902; 86587</t>
+          <t>51610; 85786</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24727; 47710</t>
+          <t>24906; 47156</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53923; 80681</t>
+          <t>58099; 85321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>57329; 91616</t>
+          <t>56822; 90311</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90908; 130133</t>
+          <t>90397; 129929</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57665; 93549</t>
+          <t>57595; 92832</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>123010; 153331</t>
+          <t>132474; 163596</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100670; 144423</t>
+          <t>99272; 141261</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153407; 204693</t>
+          <t>152734; 206904</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>89042; 132399</t>
+          <t>88641; 128668</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>185966; 225323</t>
+          <t>197983; 240086</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104212</t>
+          <t>107135</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>116987</t>
+          <t>128761</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>221199</t>
+          <t>235896</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15663; 36907</t>
+          <t>15163; 35184</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41275; 72720</t>
+          <t>42152; 72960</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35230; 66171</t>
+          <t>35742; 65320</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72493; 128812</t>
+          <t>91775; 127927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31066; 56158</t>
+          <t>29633; 56241</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40912; 74819</t>
+          <t>41670; 73670</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40018; 68616</t>
+          <t>39641; 70714</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83963; 140056</t>
+          <t>111794; 146733</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50614; 83380</t>
+          <t>52344; 81923</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90636; 137830</t>
+          <t>92051; 138259</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81632; 123328</t>
+          <t>80853; 124578</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>178467; 256143</t>
+          <t>211461; 264148</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36879</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30533</t>
+          <t>35633</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67412</t>
+          <t>77811</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9323; 26517</t>
+          <t>8463; 25007</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9702; 29048</t>
+          <t>9502; 30396</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8123; 26055</t>
+          <t>7851; 25433</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27408; 48219</t>
+          <t>32078; 56264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2912; 13681</t>
+          <t>2919; 13698</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15622; 35476</t>
+          <t>15662; 36100</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10748; 28768</t>
+          <t>9882; 28798</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23324; 40767</t>
+          <t>27519; 46306</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15062; 33215</t>
+          <t>15016; 34516</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30034; 57533</t>
+          <t>29280; 59224</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21516; 47589</t>
+          <t>21508; 46271</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54955; 82657</t>
+          <t>64203; 93396</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207493</t>
+          <t>219764</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>285921</t>
+          <t>312051</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>493414</t>
+          <t>531815</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70576; 106821</t>
+          <t>70173; 105971</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>117935; 167980</t>
+          <t>117823; 165599</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80671; 118891</t>
+          <t>80862; 121689</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>158642; 242572</t>
+          <t>194517; 248788</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>101559; 142806</t>
+          <t>102113; 142944</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>165935; 221620</t>
+          <t>163640; 218267</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>120814; 171423</t>
+          <t>121789; 172967</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>228482; 318775</t>
+          <t>285878; 338123</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181139; 237608</t>
+          <t>182237; 239500</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>293730; 370045</t>
+          <t>294564; 370769</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>213629; 275331</t>
+          <t>214066; 276682</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>426520; 546982</t>
+          <t>499886; 571073</t>
         </is>
       </c>
     </row>
